--- a/Reporte_gastos/tabla_gastos_zonas_2026-2.xlsx
+++ b/Reporte_gastos/tabla_gastos_zonas_2026-2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">TIENDA</t>
   </si>
@@ -21,6 +21,15 @@
   </si>
   <si>
     <t xml:space="preserve">Sueldos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incentivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribuciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_sueldos</t>
   </si>
   <si>
     <t xml:space="preserve">Alquileres</t>
@@ -425,326 +434,461 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>56105566.22</v>
       </c>
       <c r="C2" t="n">
+        <v>3063066.5800097</v>
+      </c>
+      <c r="D2" t="n">
+        <v>181129</v>
+      </c>
+      <c r="E2" t="n">
+        <v>991414.896205064</v>
+      </c>
+      <c r="F2" t="n">
         <v>4235610.47621476</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>7100000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>482850.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>7582850.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>2075480.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
         <v>20943355.21</v>
       </c>
       <c r="C3" t="n">
+        <v>2392026.85460177</v>
+      </c>
+      <c r="D3" t="n">
+        <v>105508</v>
+      </c>
+      <c r="E3" t="n">
+        <v>759328.647787345</v>
+      </c>
+      <c r="F3" t="n">
         <v>3256863.50238911</v>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="n">
         <v>2300000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>2339286.6</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>4639286.6</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>505129.77</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
         <v>77048921.43</v>
       </c>
       <c r="C4" t="n">
+        <v>5455093.43461147</v>
+      </c>
+      <c r="D4" t="n">
+        <v>286637</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1750743.54399241</v>
+      </c>
+      <c r="F4" t="n">
         <v>7492473.97860388</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
         <v>9400000</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>2822137.1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>12222137.1</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>2580609.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>30438640.07</v>
       </c>
       <c r="C5" t="n">
+        <v>1880886.4922549</v>
+      </c>
+      <c r="D5" t="n">
+        <v>107528</v>
+      </c>
+      <c r="E5" t="n">
+        <v>605898.704220735</v>
+      </c>
+      <c r="F5" t="n">
         <v>2594313.19647564</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
         <v>2622347.04</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>576451.13</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>3198798.17</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>360694.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
         <v>16278681.88</v>
       </c>
       <c r="C6" t="n">
+        <v>2114828.63823529</v>
+      </c>
+      <c r="D6" t="n">
+        <v>92420</v>
+      </c>
+      <c r="E6" t="n">
+        <v>671740.176730294</v>
+      </c>
+      <c r="F6" t="n">
         <v>2878988.81496559</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>850000</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>334847.68</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>1184847.68</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>993046.52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
         <v>46717321.95</v>
       </c>
       <c r="C7" t="n">
+        <v>3995715.1304902</v>
+      </c>
+      <c r="D7" t="n">
+        <v>199948</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1277638.88095103</v>
+      </c>
+      <c r="F7" t="n">
         <v>5473302.01144123</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>3472347.04</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>911298.81</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>4383645.85</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>1353741.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>2967396.82</v>
       </c>
       <c r="C8" t="n">
+        <v>1252334.49995375</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22505</v>
+      </c>
+      <c r="E8" t="n">
+        <v>390541.572652102</v>
+      </c>
+      <c r="F8" t="n">
         <v>1665381.07260585</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>715965.54</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>372670.03</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>1088635.57</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>296430</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>12951444.02</v>
       </c>
       <c r="C9" t="n">
+        <v>1987749.5095098</v>
+      </c>
+      <c r="D9" t="n">
+        <v>59138</v>
+      </c>
+      <c r="E9" t="n">
+        <v>627251.06736897</v>
+      </c>
+      <c r="F9" t="n">
         <v>2674138.57687877</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>1473060.3</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>576451.13</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>2049511.43</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>389877.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
         <v>15918840.84</v>
       </c>
       <c r="C10" t="n">
+        <v>3240084.00946355</v>
+      </c>
+      <c r="D10" t="n">
+        <v>81643</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1017792.64002107</v>
+      </c>
+      <c r="F10" t="n">
         <v>4339519.64948462</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
         <v>2189025.84</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>949121.16</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>3138147</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>686307.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>9447799.86</v>
       </c>
       <c r="C11" t="n">
+        <v>1463143.61080284</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35380</v>
+      </c>
+      <c r="E11" t="n">
+        <v>448478.3049048</v>
+      </c>
+      <c r="F11" t="n">
         <v>1947001.91570764</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="n">
         <v>511403.96</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>57016.04</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>568420</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>44957.72</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>7961629.92</v>
       </c>
       <c r="C12" t="n">
+        <v>2574637.49919717</v>
+      </c>
+      <c r="D12" t="n">
+        <v>34275</v>
+      </c>
+      <c r="E12" t="n">
+        <v>785929.0613402</v>
+      </c>
+      <c r="F12" t="n">
         <v>3394841.56053737</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>1619513.17</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>163587.19</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>1783100.36</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>42642.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="n">
         <v>17409429.78</v>
       </c>
       <c r="C13" t="n">
+        <v>4037781.11</v>
+      </c>
+      <c r="D13" t="n">
+        <v>69655</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1234407.366245</v>
+      </c>
+      <c r="F13" t="n">
         <v>5341843.476245</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
         <v>2130917.13</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>220603.23</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>2351520.36</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>87600.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
         <v>13799296.42</v>
       </c>
       <c r="C14" t="n">
+        <v>1868489.65</v>
+      </c>
+      <c r="D14" t="n">
+        <v>34615</v>
+      </c>
+      <c r="E14" t="n">
+        <v>577866.741685</v>
+      </c>
+      <c r="F14" t="n">
         <v>2480971.391685</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
         <v>1199300.67</v>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>1152902.26</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>2352202.93</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>465922.85</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
         <v>170893810.42</v>
       </c>
       <c r="C15" t="n">
+        <v>18597163.3345652</v>
+      </c>
+      <c r="D15" t="n">
+        <v>672498</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5858449.17289451</v>
+      </c>
+      <c r="F15" t="n">
         <v>25128110.5074597</v>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" t="n">
         <v>18391590.68</v>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>6056062.56</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>24447653.24</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>5174182.42</v>
       </c>
     </row>
